--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -6,6 +6,8 @@
   </bookViews>
   <sheets>
     <sheet name="Frazaro" sheetId="1" r:id="rIdFrazaro1"/>
+    <sheet name="Output" sheetId="2" r:id="rIdFrazaro2"/>
+    <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -194,4 +196,58 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/frazaro_2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0">
+        <f t="shared" ref="C2:C4" si="0">B2+B3</f>
+      </c>
+      <c r="D2" s="0">
+        <f>_xlfn.IFS(B2&gt;3,"big",TRUE,"small")</f>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="0">
+        <f>B2*2</f>
+      </c>
+      <c r="C3" s="0">
+        <f t="shared" si="0"/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="0">
+        <f t="shared" si="0"/>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/frazaro_3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">west</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -9,8 +9,33 @@
     <sheet name="Output" sheetId="2" r:id="rIdFrazaro2"/>
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
+  <definedNames>
+    <definedName name="Frazaro.Build">"Frazaro 0.7.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -215,8 +240,8 @@
       <c r="C2" s="0">
         <f t="shared" ref="C2:C4" si="0">B2+B3</f>
       </c>
-      <c r="D2" s="0">
-        <f>_xlfn.IFS(B2&gt;3,"big",TRUE,"small")</f>
+      <c r="D2" s="0" cm="1">
+        <f t="array" ref="D2">_xlfn.IFS(B2&gt;3,"big",TRUE,"small")</f>
       </c>
     </row>
     <row r="3">

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.7.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:519A44CC1A158698814D3376A1557A4427377687F06232886F463190B9A4EBC9 over 166410 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -239,22 +239,27 @@
       </c>
       <c r="C2" s="0">
         <f t="shared" ref="C2:C4" si="0">B2+B3</f>
-      </c>
-      <c r="D2" s="0" cm="1">
+        <v>15</v>
+      </c>
+      <c r="D2" s="0" t="str" cm="1">
         <f t="array" ref="D2">_xlfn.IFS(B2&gt;3,"big",TRUE,"small")</f>
+        <v>big</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="0">
         <f>B2*2</f>
+        <v>10</v>
       </c>
       <c r="C3" s="0">
         <f t="shared" si="0"/>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="0">
         <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.2; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.2; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.3; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.3; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.9.4; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.9.4; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.10.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.10.1; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.11.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>

--- a/scripts/build/fixture_golden.xlsx
+++ b/scripts/build/fixture_golden.xlsx
@@ -10,7 +10,7 @@
     <sheet name="data" sheetId="3" r:id="rIdFrazaro3"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.11.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.12.0; sentences sha256:1FD9186A423AE3DE72491E35768AE341491A3414FB858FF0271DDD08ACBCA1C9 over 322 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
